--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -1217,7 +1217,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124080620</v>
+        <v>124074953</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476414</v>
+        <v>476191</v>
       </c>
       <c r="R7" t="n">
-        <v>6848706</v>
+        <v>6848765</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124074953</v>
+        <v>124080620</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476191</v>
+        <v>476414</v>
       </c>
       <c r="R8" t="n">
-        <v>6848765</v>
+        <v>6848706</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124074865</v>
+        <v>124075420</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476192</v>
+        <v>476196</v>
       </c>
       <c r="R2" t="n">
-        <v>6848770</v>
+        <v>6848824</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124074891</v>
+        <v>124076461</v>
       </c>
       <c r="B3" t="n">
-        <v>78524</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476193</v>
+        <v>475915</v>
       </c>
       <c r="R3" t="n">
-        <v>6848769</v>
+        <v>6848787</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124074520</v>
+        <v>124074685</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -923,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -937,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476246</v>
+        <v>476219</v>
       </c>
       <c r="R4" t="n">
-        <v>6848753</v>
+        <v>6848800</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124075530</v>
+        <v>124074891</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>78524</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,47 +1020,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476173</v>
+        <v>476193</v>
       </c>
       <c r="R5" t="n">
-        <v>6848843</v>
+        <v>6848769</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124073883</v>
+        <v>124075578</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,41 +1122,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476276</v>
+        <v>476178</v>
       </c>
       <c r="R6" t="n">
-        <v>6848952</v>
+        <v>6848844</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,11 +1195,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,7 +1221,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124074953</v>
+        <v>124073764</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1266,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476191</v>
+        <v>476250</v>
       </c>
       <c r="R7" t="n">
-        <v>6848765</v>
+        <v>6848896</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124080620</v>
+        <v>124074865</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1363,7 +1367,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1377,13 +1381,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476414</v>
+        <v>476192</v>
       </c>
       <c r="R8" t="n">
-        <v>6848706</v>
+        <v>6848770</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,7 +1443,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124076461</v>
+        <v>124074520</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1474,7 +1478,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1488,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475915</v>
+        <v>476246</v>
       </c>
       <c r="R9" t="n">
-        <v>6848787</v>
+        <v>6848753</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,7 +1554,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124075578</v>
+        <v>124074076</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1585,7 +1589,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1599,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476178</v>
+        <v>476230</v>
       </c>
       <c r="R10" t="n">
-        <v>6848844</v>
+        <v>6848906</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1661,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124075420</v>
+        <v>124080620</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1696,7 +1700,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1710,13 +1714,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476196</v>
+        <v>476414</v>
       </c>
       <c r="R11" t="n">
-        <v>6848824</v>
+        <v>6848706</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124074076</v>
+        <v>124073883</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1784,50 +1788,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476230</v>
+        <v>476276</v>
       </c>
       <c r="R12" t="n">
-        <v>6848906</v>
+        <v>6848952</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,6 +1852,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,7 +1883,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124073764</v>
+        <v>124074025</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1932,13 +1932,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476250</v>
+        <v>476236</v>
       </c>
       <c r="R13" t="n">
-        <v>6848896</v>
+        <v>6848928</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124074685</v>
+        <v>124074953</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2043,13 +2043,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476219</v>
+        <v>476191</v>
       </c>
       <c r="R14" t="n">
-        <v>6848800</v>
+        <v>6848765</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124074025</v>
+        <v>124075530</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476236</v>
+        <v>476173</v>
       </c>
       <c r="R15" t="n">
-        <v>6848928</v>
+        <v>6848843</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2214,6 +2214,117 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124178185</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56090</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gryssjökojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>475998</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6848920</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124076461</v>
+        <v>124075530</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475915</v>
+        <v>476173</v>
       </c>
       <c r="R3" t="n">
-        <v>6848787</v>
+        <v>6848843</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124074685</v>
+        <v>124080620</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476219</v>
+        <v>476414</v>
       </c>
       <c r="R4" t="n">
-        <v>6848800</v>
+        <v>6848706</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124074891</v>
+        <v>124074025</v>
       </c>
       <c r="B5" t="n">
-        <v>78524</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,41 +1020,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476193</v>
+        <v>476236</v>
       </c>
       <c r="R5" t="n">
-        <v>6848769</v>
+        <v>6848928</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124075578</v>
+        <v>124073764</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1145,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1159,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476178</v>
+        <v>476250</v>
       </c>
       <c r="R6" t="n">
-        <v>6848844</v>
+        <v>6848896</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124073764</v>
+        <v>124074520</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1256,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1270,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476250</v>
+        <v>476246</v>
       </c>
       <c r="R7" t="n">
-        <v>6848896</v>
+        <v>6848753</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1443,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124074520</v>
+        <v>124076461</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1478,7 +1487,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1492,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476246</v>
+        <v>475915</v>
       </c>
       <c r="R9" t="n">
-        <v>6848753</v>
+        <v>6848787</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124074076</v>
+        <v>124074891</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>78524</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,50 +1575,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476230</v>
+        <v>476193</v>
       </c>
       <c r="R10" t="n">
-        <v>6848906</v>
+        <v>6848769</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124080620</v>
+        <v>124074076</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476414</v>
+        <v>476230</v>
       </c>
       <c r="R11" t="n">
-        <v>6848706</v>
+        <v>6848906</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1776,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124073883</v>
+        <v>124074953</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1788,38 +1788,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476276</v>
+        <v>476191</v>
       </c>
       <c r="R12" t="n">
-        <v>6848952</v>
+        <v>6848765</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,11 +1861,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124074025</v>
+        <v>124073883</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1895,50 +1899,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476236</v>
+        <v>476276</v>
       </c>
       <c r="R13" t="n">
-        <v>6848928</v>
+        <v>6848952</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1968,6 +1963,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,7 +1994,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124074953</v>
+        <v>124074685</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2043,13 +2043,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476191</v>
+        <v>476219</v>
       </c>
       <c r="R14" t="n">
-        <v>6848765</v>
+        <v>6848800</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124075530</v>
+        <v>124075578</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476173</v>
+        <v>476178</v>
       </c>
       <c r="R15" t="n">
-        <v>6848843</v>
+        <v>6848844</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124074865</v>
+        <v>124075420</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476192</v>
+        <v>476196</v>
       </c>
       <c r="R2" t="n">
-        <v>6848770</v>
+        <v>6848824</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124074076</v>
+        <v>124074025</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476230</v>
+        <v>476236</v>
       </c>
       <c r="R3" t="n">
-        <v>6848906</v>
+        <v>6848928</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124075578</v>
+        <v>124073764</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476178</v>
+        <v>476250</v>
       </c>
       <c r="R4" t="n">
-        <v>6848844</v>
+        <v>6848896</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124073883</v>
+        <v>124074076</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,41 +1020,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476276</v>
+        <v>476230</v>
       </c>
       <c r="R5" t="n">
-        <v>6848952</v>
+        <v>6848906</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,11 +1093,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124076461</v>
+        <v>124074953</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1150,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1164,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475915</v>
+        <v>476191</v>
       </c>
       <c r="R6" t="n">
-        <v>6848787</v>
+        <v>6848765</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124074685</v>
+        <v>124076461</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1261,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1275,13 +1279,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476219</v>
+        <v>475915</v>
       </c>
       <c r="R7" t="n">
-        <v>6848800</v>
+        <v>6848787</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124080620</v>
+        <v>124074865</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1372,7 +1376,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1386,13 +1390,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476414</v>
+        <v>476192</v>
       </c>
       <c r="R8" t="n">
-        <v>6848706</v>
+        <v>6848770</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1448,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124075530</v>
+        <v>124074685</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1483,7 +1487,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1497,13 +1501,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476173</v>
+        <v>476219</v>
       </c>
       <c r="R9" t="n">
-        <v>6848843</v>
+        <v>6848800</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1559,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124074520</v>
+        <v>124074891</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,47 +1575,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476246</v>
+        <v>476193</v>
       </c>
       <c r="R10" t="n">
-        <v>6848753</v>
+        <v>6848769</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124074025</v>
+        <v>124075530</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1705,7 +1700,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1719,13 +1714,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476236</v>
+        <v>476173</v>
       </c>
       <c r="R11" t="n">
-        <v>6848928</v>
+        <v>6848843</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,7 +1776,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124074953</v>
+        <v>124074520</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1816,7 +1811,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1830,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476191</v>
+        <v>476246</v>
       </c>
       <c r="R12" t="n">
-        <v>6848765</v>
+        <v>6848753</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1887,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124073764</v>
+        <v>124080620</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1927,7 +1922,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1941,13 +1936,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476250</v>
+        <v>476414</v>
       </c>
       <c r="R13" t="n">
-        <v>6848896</v>
+        <v>6848706</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2003,10 +1998,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124074891</v>
+        <v>124073883</v>
       </c>
       <c r="B14" t="n">
-        <v>78546</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,21 +2014,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476193</v>
+        <v>476276</v>
       </c>
       <c r="R14" t="n">
-        <v>6848769</v>
+        <v>6848952</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,6 +2074,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,7 +2105,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124075420</v>
+        <v>124075578</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476196</v>
+        <v>476178</v>
       </c>
       <c r="R15" t="n">
-        <v>6848824</v>
+        <v>6848844</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124074025</v>
+        <v>124076461</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476236</v>
+        <v>475915</v>
       </c>
       <c r="R3" t="n">
-        <v>6848928</v>
+        <v>6848787</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124073764</v>
+        <v>124074520</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476250</v>
+        <v>476246</v>
       </c>
       <c r="R4" t="n">
-        <v>6848896</v>
+        <v>6848753</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124074076</v>
+        <v>124073883</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,50 +1020,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476230</v>
+        <v>476276</v>
       </c>
       <c r="R5" t="n">
-        <v>6848906</v>
+        <v>6848952</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,6 +1084,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124074953</v>
+        <v>124074685</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1154,7 +1150,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1168,13 +1164,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476191</v>
+        <v>476219</v>
       </c>
       <c r="R6" t="n">
-        <v>6848765</v>
+        <v>6848800</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124076461</v>
+        <v>124074891</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,47 +1238,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475915</v>
+        <v>476193</v>
       </c>
       <c r="R7" t="n">
-        <v>6848787</v>
+        <v>6848769</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1328,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124074865</v>
+        <v>124075530</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1376,7 +1363,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1390,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476192</v>
+        <v>476173</v>
       </c>
       <c r="R8" t="n">
-        <v>6848770</v>
+        <v>6848843</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124074685</v>
+        <v>124074076</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1487,7 +1474,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1501,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476219</v>
+        <v>476230</v>
       </c>
       <c r="R9" t="n">
-        <v>6848800</v>
+        <v>6848906</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1563,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124074891</v>
+        <v>124073764</v>
       </c>
       <c r="B10" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,38 +1562,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476193</v>
+        <v>476250</v>
       </c>
       <c r="R10" t="n">
-        <v>6848769</v>
+        <v>6848896</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1661,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124075530</v>
+        <v>124075578</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1700,7 +1696,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1714,13 +1710,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476173</v>
+        <v>476178</v>
       </c>
       <c r="R11" t="n">
-        <v>6848843</v>
+        <v>6848844</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,7 +1772,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124074520</v>
+        <v>124080620</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1811,7 +1807,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1825,13 +1821,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476246</v>
+        <v>476414</v>
       </c>
       <c r="R12" t="n">
-        <v>6848753</v>
+        <v>6848706</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1887,7 +1883,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124080620</v>
+        <v>124074865</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1922,7 +1918,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1936,13 +1932,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476414</v>
+        <v>476192</v>
       </c>
       <c r="R13" t="n">
-        <v>6848706</v>
+        <v>6848770</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1998,10 +1994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124073883</v>
+        <v>124074953</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2010,38 +2006,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476276</v>
+        <v>476191</v>
       </c>
       <c r="R14" t="n">
-        <v>6848952</v>
+        <v>6848765</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,11 +2079,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,7 +2105,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124075578</v>
+        <v>124074025</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476178</v>
+        <v>476236</v>
       </c>
       <c r="R15" t="n">
-        <v>6848844</v>
+        <v>6848928</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124075420</v>
+        <v>124074953</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476196</v>
+        <v>476191</v>
       </c>
       <c r="R2" t="n">
-        <v>6848824</v>
+        <v>6848765</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124076461</v>
+        <v>124074025</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475915</v>
+        <v>476236</v>
       </c>
       <c r="R3" t="n">
-        <v>6848787</v>
+        <v>6848928</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124074520</v>
+        <v>124080620</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476246</v>
+        <v>476414</v>
       </c>
       <c r="R4" t="n">
-        <v>6848753</v>
+        <v>6848706</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124074685</v>
+        <v>124074865</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1164,13 +1164,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476219</v>
+        <v>476192</v>
       </c>
       <c r="R6" t="n">
-        <v>6848800</v>
+        <v>6848770</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124074891</v>
+        <v>124075420</v>
       </c>
       <c r="B7" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,41 +1238,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476193</v>
+        <v>476196</v>
       </c>
       <c r="R7" t="n">
-        <v>6848769</v>
+        <v>6848824</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124075530</v>
+        <v>124076461</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1363,7 +1372,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1377,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476173</v>
+        <v>475915</v>
       </c>
       <c r="R8" t="n">
-        <v>6848843</v>
+        <v>6848787</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,10 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124074076</v>
+        <v>124074891</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,50 +1460,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476230</v>
+        <v>476193</v>
       </c>
       <c r="R9" t="n">
-        <v>6848906</v>
+        <v>6848769</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124080620</v>
+        <v>124074520</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1821,13 +1821,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476414</v>
+        <v>476246</v>
       </c>
       <c r="R12" t="n">
-        <v>6848706</v>
+        <v>6848753</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124074865</v>
+        <v>124074076</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1932,13 +1932,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476192</v>
+        <v>476230</v>
       </c>
       <c r="R13" t="n">
-        <v>6848770</v>
+        <v>6848906</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124074953</v>
+        <v>124075530</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476191</v>
+        <v>476173</v>
       </c>
       <c r="R14" t="n">
-        <v>6848765</v>
+        <v>6848843</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2105,7 +2105,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124074025</v>
+        <v>124074685</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476236</v>
+        <v>476219</v>
       </c>
       <c r="R15" t="n">
-        <v>6848928</v>
+        <v>6848800</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124074025</v>
+        <v>124074076</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476236</v>
+        <v>476230</v>
       </c>
       <c r="R3" t="n">
-        <v>6848928</v>
+        <v>6848906</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124080620</v>
+        <v>124074891</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,50 +909,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476414</v>
+        <v>476193</v>
       </c>
       <c r="R4" t="n">
-        <v>6848706</v>
+        <v>6848769</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124073883</v>
+        <v>124074685</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,41 +1011,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476276</v>
+        <v>476219</v>
       </c>
       <c r="R5" t="n">
-        <v>6848952</v>
+        <v>6848800</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,11 +1084,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124074865</v>
+        <v>124075420</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1150,7 +1145,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1164,13 +1159,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476192</v>
+        <v>476196</v>
       </c>
       <c r="R6" t="n">
-        <v>6848770</v>
+        <v>6848824</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1221,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124075420</v>
+        <v>124074865</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1261,7 +1256,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1275,13 +1270,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476196</v>
+        <v>476192</v>
       </c>
       <c r="R7" t="n">
-        <v>6848824</v>
+        <v>6848770</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1448,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124074891</v>
+        <v>124074520</v>
       </c>
       <c r="B9" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,38 +1455,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476193</v>
+        <v>476246</v>
       </c>
       <c r="R9" t="n">
-        <v>6848769</v>
+        <v>6848753</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,7 +1554,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124073764</v>
+        <v>124075530</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1585,7 +1589,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1599,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476250</v>
+        <v>476173</v>
       </c>
       <c r="R10" t="n">
-        <v>6848896</v>
+        <v>6848843</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124075578</v>
+        <v>124074025</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1696,7 +1700,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1710,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476178</v>
+        <v>476236</v>
       </c>
       <c r="R11" t="n">
-        <v>6848844</v>
+        <v>6848928</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1772,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124074520</v>
+        <v>124073883</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1784,47 +1788,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476246</v>
+        <v>476276</v>
       </c>
       <c r="R12" t="n">
-        <v>6848753</v>
+        <v>6848952</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,6 +1852,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,7 +1883,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124074076</v>
+        <v>124075578</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476230</v>
+        <v>476178</v>
       </c>
       <c r="R13" t="n">
-        <v>6848906</v>
+        <v>6848844</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124075530</v>
+        <v>124073764</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476173</v>
+        <v>476250</v>
       </c>
       <c r="R14" t="n">
-        <v>6848843</v>
+        <v>6848896</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2105,7 +2105,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124074685</v>
+        <v>124080620</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476219</v>
+        <v>476414</v>
       </c>
       <c r="R15" t="n">
-        <v>6848800</v>
+        <v>6848706</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -1332,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124076461</v>
+        <v>124074520</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475915</v>
+        <v>476246</v>
       </c>
       <c r="R8" t="n">
-        <v>6848787</v>
+        <v>6848753</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124074520</v>
+        <v>124076461</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476246</v>
+        <v>475915</v>
       </c>
       <c r="R9" t="n">
-        <v>6848753</v>
+        <v>6848787</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124074953</v>
+        <v>124075420</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476191</v>
+        <v>476196</v>
       </c>
       <c r="R2" t="n">
-        <v>6848765</v>
+        <v>6848824</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124074076</v>
+        <v>124074520</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476230</v>
+        <v>476246</v>
       </c>
       <c r="R3" t="n">
-        <v>6848906</v>
+        <v>6848753</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124074891</v>
+        <v>124074025</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,41 +909,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476193</v>
+        <v>476236</v>
       </c>
       <c r="R4" t="n">
-        <v>6848769</v>
+        <v>6848928</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1110,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124075420</v>
+        <v>124075530</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1145,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1159,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476196</v>
+        <v>476173</v>
       </c>
       <c r="R6" t="n">
-        <v>6848824</v>
+        <v>6848843</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1332,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124074520</v>
+        <v>124080620</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1367,7 +1376,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1381,13 +1390,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476246</v>
+        <v>476414</v>
       </c>
       <c r="R8" t="n">
-        <v>6848753</v>
+        <v>6848706</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1443,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124076461</v>
+        <v>124074891</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1455,47 +1464,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475915</v>
+        <v>476193</v>
       </c>
       <c r="R9" t="n">
-        <v>6848787</v>
+        <v>6848769</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124075530</v>
+        <v>124073764</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476173</v>
+        <v>476250</v>
       </c>
       <c r="R10" t="n">
-        <v>6848843</v>
+        <v>6848896</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124074025</v>
+        <v>124074953</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476236</v>
+        <v>476191</v>
       </c>
       <c r="R11" t="n">
-        <v>6848928</v>
+        <v>6848765</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124073764</v>
+        <v>124074076</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2043,13 +2043,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476250</v>
+        <v>476230</v>
       </c>
       <c r="R14" t="n">
-        <v>6848896</v>
+        <v>6848906</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124080620</v>
+        <v>124076461</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476414</v>
+        <v>475915</v>
       </c>
       <c r="R15" t="n">
-        <v>6848706</v>
+        <v>6848787</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -1776,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124073883</v>
+        <v>124075578</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1788,41 +1788,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476276</v>
+        <v>476178</v>
       </c>
       <c r="R12" t="n">
-        <v>6848952</v>
+        <v>6848844</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,11 +1861,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124075578</v>
+        <v>124073883</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1895,50 +1899,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476178</v>
+        <v>476276</v>
       </c>
       <c r="R13" t="n">
-        <v>6848844</v>
+        <v>6848952</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1968,6 +1963,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124075420</v>
+        <v>124074953</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476196</v>
+        <v>476191</v>
       </c>
       <c r="R2" t="n">
-        <v>6848824</v>
+        <v>6848765</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124074520</v>
+        <v>124074685</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476246</v>
+        <v>476219</v>
       </c>
       <c r="R3" t="n">
-        <v>6848753</v>
+        <v>6848800</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124074025</v>
+        <v>124074076</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476236</v>
+        <v>476230</v>
       </c>
       <c r="R4" t="n">
-        <v>6848928</v>
+        <v>6848906</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124074685</v>
+        <v>124073764</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476219</v>
+        <v>476250</v>
       </c>
       <c r="R5" t="n">
-        <v>6848800</v>
+        <v>6848896</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124075530</v>
+        <v>124076461</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476173</v>
+        <v>475915</v>
       </c>
       <c r="R6" t="n">
-        <v>6848843</v>
+        <v>6848787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124080620</v>
+        <v>124075530</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1390,13 +1390,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476414</v>
+        <v>476173</v>
       </c>
       <c r="R8" t="n">
-        <v>6848706</v>
+        <v>6848843</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124074891</v>
+        <v>124075420</v>
       </c>
       <c r="B9" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,41 +1464,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476193</v>
+        <v>476196</v>
       </c>
       <c r="R9" t="n">
-        <v>6848769</v>
+        <v>6848824</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124073764</v>
+        <v>124074025</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1589,7 +1598,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1603,13 +1612,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476250</v>
+        <v>476236</v>
       </c>
       <c r="R10" t="n">
-        <v>6848896</v>
+        <v>6848928</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124074953</v>
+        <v>124080620</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1700,7 +1709,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1714,13 +1723,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476191</v>
+        <v>476414</v>
       </c>
       <c r="R11" t="n">
-        <v>6848765</v>
+        <v>6848706</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124075578</v>
+        <v>124073883</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1788,50 +1797,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476178</v>
+        <v>476276</v>
       </c>
       <c r="R12" t="n">
-        <v>6848844</v>
+        <v>6848952</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,6 +1861,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124073883</v>
+        <v>124074891</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>78546</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,21 +1908,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476276</v>
+        <v>476193</v>
       </c>
       <c r="R13" t="n">
-        <v>6848952</v>
+        <v>6848769</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,11 +1968,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,7 +1994,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124074076</v>
+        <v>124074520</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2043,13 +2043,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476230</v>
+        <v>476246</v>
       </c>
       <c r="R14" t="n">
-        <v>6848906</v>
+        <v>6848753</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124076461</v>
+        <v>124075578</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475915</v>
+        <v>476178</v>
       </c>
       <c r="R15" t="n">
-        <v>6848787</v>
+        <v>6848844</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124074685</v>
+        <v>124075420</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476219</v>
+        <v>476196</v>
       </c>
       <c r="R3" t="n">
-        <v>6848800</v>
+        <v>6848824</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124074076</v>
+        <v>124075530</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476230</v>
+        <v>476173</v>
       </c>
       <c r="R4" t="n">
-        <v>6848906</v>
+        <v>6848843</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124073764</v>
+        <v>124080620</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476250</v>
+        <v>476414</v>
       </c>
       <c r="R5" t="n">
-        <v>6848896</v>
+        <v>6848706</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124076461</v>
+        <v>124074520</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475915</v>
+        <v>476246</v>
       </c>
       <c r="R6" t="n">
-        <v>6848787</v>
+        <v>6848753</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124074865</v>
+        <v>124073883</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,47 +1242,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476192</v>
+        <v>476276</v>
       </c>
       <c r="R7" t="n">
-        <v>6848770</v>
+        <v>6848952</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,6 +1306,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124075530</v>
+        <v>124074891</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,47 +1349,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476173</v>
+        <v>476193</v>
       </c>
       <c r="R8" t="n">
-        <v>6848843</v>
+        <v>6848769</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124075420</v>
+        <v>124075578</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1487,7 +1474,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1501,13 +1488,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476196</v>
+        <v>476178</v>
       </c>
       <c r="R9" t="n">
-        <v>6848824</v>
+        <v>6848844</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1674,7 +1661,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124080620</v>
+        <v>124074685</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1709,7 +1696,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1723,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476414</v>
+        <v>476219</v>
       </c>
       <c r="R11" t="n">
-        <v>6848706</v>
+        <v>6848800</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1785,10 +1772,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124073883</v>
+        <v>124073764</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,38 +1784,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476276</v>
+        <v>476250</v>
       </c>
       <c r="R12" t="n">
-        <v>6848952</v>
+        <v>6848896</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1861,11 +1857,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1883,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124074891</v>
+        <v>124074076</v>
       </c>
       <c r="B13" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,41 +1895,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476193</v>
+        <v>476230</v>
       </c>
       <c r="R13" t="n">
-        <v>6848769</v>
+        <v>6848906</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124074520</v>
+        <v>124076461</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476246</v>
+        <v>475915</v>
       </c>
       <c r="R14" t="n">
-        <v>6848753</v>
+        <v>6848787</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2105,7 +2105,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124075578</v>
+        <v>124074865</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476178</v>
+        <v>476192</v>
       </c>
       <c r="R15" t="n">
-        <v>6848844</v>
+        <v>6848770</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124074953</v>
+        <v>124074891</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476191</v>
+        <v>476193</v>
       </c>
       <c r="R2" t="n">
-        <v>6848765</v>
+        <v>6848769</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,62 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124075420</v>
+        <v>124073883</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476196</v>
+        <v>476276</v>
       </c>
       <c r="R3" t="n">
-        <v>6848824</v>
+        <v>6848952</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,62 +874,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124075530</v>
+        <v>124178185</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+          <t>Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476173</v>
+        <v>475998</v>
       </c>
       <c r="R4" t="n">
-        <v>6848843</v>
+        <v>6848920</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,15 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124080620</v>
+        <v>124073764</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,7 +1010,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,13 +1024,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476414</v>
+        <v>476250</v>
       </c>
       <c r="R5" t="n">
-        <v>6848706</v>
+        <v>6848896</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,15 +1086,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124074520</v>
+        <v>124074025</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,7 +1116,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1168,13 +1130,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476246</v>
+        <v>476236</v>
       </c>
       <c r="R6" t="n">
-        <v>6848753</v>
+        <v>6848928</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,53 +1192,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124073883</v>
+        <v>124074076</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476276</v>
+        <v>476230</v>
       </c>
       <c r="R7" t="n">
-        <v>6848952</v>
+        <v>6848906</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1306,11 +1272,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,50 +1298,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124074891</v>
+        <v>124074520</v>
       </c>
       <c r="B8" t="n">
-        <v>78546</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476193</v>
+        <v>476246</v>
       </c>
       <c r="R8" t="n">
-        <v>6848769</v>
+        <v>6848753</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,15 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124075578</v>
+        <v>124074685</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1434,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1488,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476178</v>
+        <v>476219</v>
       </c>
       <c r="R9" t="n">
-        <v>6848844</v>
+        <v>6848800</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1550,15 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124074025</v>
+        <v>124074865</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,7 +1540,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1599,13 +1554,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476236</v>
+        <v>476192</v>
       </c>
       <c r="R10" t="n">
-        <v>6848928</v>
+        <v>6848770</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1661,15 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124074685</v>
+        <v>124074953</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,7 +1646,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1710,13 +1660,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476219</v>
+        <v>476191</v>
       </c>
       <c r="R11" t="n">
-        <v>6848800</v>
+        <v>6848765</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,15 +1722,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124073764</v>
+        <v>124075209</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,7 +1752,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1821,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476250</v>
+        <v>476158</v>
       </c>
       <c r="R12" t="n">
-        <v>6848896</v>
+        <v>6848774</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,15 +1828,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124074076</v>
+        <v>124075420</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1858,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1932,13 +1872,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476230</v>
+        <v>476196</v>
       </c>
       <c r="R13" t="n">
-        <v>6848906</v>
+        <v>6848824</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,15 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124076461</v>
+        <v>124075530</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +1964,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2043,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475915</v>
+        <v>476173</v>
       </c>
       <c r="R14" t="n">
-        <v>6848787</v>
+        <v>6848843</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2105,15 +2040,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124074865</v>
+        <v>124075578</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,7 +2070,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2154,13 +2084,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476192</v>
+        <v>476178</v>
       </c>
       <c r="R15" t="n">
-        <v>6848770</v>
+        <v>6848844</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2216,62 +2146,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124178185</v>
+        <v>124076146</v>
       </c>
       <c r="B16" t="n">
-        <v>56112</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gryssjökojan, Dlr</t>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475998</v>
+        <v>476040</v>
       </c>
       <c r="R16" t="n">
-        <v>6848920</v>
+        <v>6848764</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2295,12 +2220,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2324,6 +2249,218 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124076461</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>475915</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6848787</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124080620</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gryssjökojan, Gryssjökojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>476414</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6848706</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30608-2023 artfynd.xlsx
+++ b/artfynd/A 30608-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124074891</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124073883</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124178185</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124073764</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124074025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124074076</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124074520</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1507,6 +1547,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124074685</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124074865</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1719,6 +1769,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124074953</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1825,6 +1880,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124075209</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1931,6 +1991,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124075420</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2037,6 +2102,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124075530</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2143,6 +2213,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124075578</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2249,6 +2324,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124076146</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2355,6 +2435,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124076461</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2461,8 +2546,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124080620</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>